--- a/lessons/sorting/excels/remarks_lcs_star.xlsx
+++ b/lessons/sorting/excels/remarks_lcs_star.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~0.00, -direction (10:22:01.758) ~0.11, -column (10:22:03.223) ~0.17, -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.00, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+        <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,12 +187,12 @@
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+        <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -212,17 +212,17 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>-center (10:17:20.707), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +flex (00:00:00)</t>
+        <t>-center (10:17:20.707) ~0.17, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~0.14, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +flex (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
@@ -247,7 +247,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -262,7 +262,7 @@
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
@@ -287,17 +287,17 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -0px (10:48:03.827), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -0px (10:48:03.827) ~0.33, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+        <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -317,7 +317,7 @@
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
@@ -342,12 +342,12 @@
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -367,7 +367,7 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -387,17 +387,17 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+        <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+        <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -417,17 +417,17 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+        <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -447,12 +447,12 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00)</t>
+        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D45" authorId="0" shapeId="0">
@@ -477,7 +477,7 @@
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
@@ -502,7 +502,7 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -517,17 +517,17 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -547,17 +547,17 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (10:12:23.484), +htm (00:00:00)</t>
+        <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -577,7 +577,7 @@
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -602,12 +602,12 @@
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -627,17 +627,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -657,7 +657,7 @@
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -677,7 +677,7 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
@@ -702,12 +702,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:20:09.451), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -0px (10:48:03.827), +:* (10:50:08.734), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+        <t>-; (10:20:09.451) ~1.00, -display (10:47:38.305) ~1.00, -: (10:47:38.437), -flex (10:47:39.551) ~1.00, -0px (10:48:03.827) ~0.33, +:* (10:50:08.734), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -1 (10:59:28.458), -- (10:59:44.058), -1 (10:59:44.656), -- (11:01:07.252), -1 (11:01:07.757), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -1 (10:59:28.458) ~0.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -727,17 +727,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+        <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -200px (10:20:09.051), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -background (10:44:24.231), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -200px (10:20:09.051) ~0.80, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -background (10:44:24.231) ~0.90, +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -752,7 +752,7 @@
     </comment>
     <comment ref="O71" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q71" authorId="0" shapeId="0">
@@ -777,17 +777,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -123456 (10:19:55.544), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +654321 (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -123456 (10:19:55.544) ~0.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -807,7 +807,7 @@
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -822,12 +822,12 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -847,7 +847,7 @@
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q78" authorId="0" shapeId="0">
@@ -872,12 +872,12 @@
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -897,7 +897,7 @@
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q81" authorId="0" shapeId="0">
@@ -922,12 +922,12 @@
     </comment>
     <comment ref="M82" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:17:06.867), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
+        <t>-&lt; (10:12:37.377), -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:17:06.867), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -947,7 +947,7 @@
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~0.00, -direction (10:22:01.758) ~0.11, -column (10:22:03.223) ~0.17, -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.00, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+          <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+          <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-center (10:17:20.707), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +flex (00:00:00)</t>
+          <t>-center (10:17:20.707) ~0.17, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~0.14, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +flex (00:00:00)</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -0px (10:48:03.827), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -0px (10:48:03.827) ~0.33, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+          <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+          <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+          <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+          <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00)</t>
+          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (10:12:23.484), +htm (00:00:00)</t>
+          <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-; (10:20:09.451), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -0px (10:48:03.827), +:* (10:50:08.734), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+          <t>-; (10:20:09.451) ~1.00, -display (10:47:38.305) ~1.00, -: (10:47:38.437), -flex (10:47:39.551) ~1.00, -0px (10:48:03.827) ~0.33, +:* (10:50:08.734), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -1 (10:59:28.458), -- (10:59:44.058), -1 (10:59:44.656), -- (11:01:07.252), -1 (11:01:07.757), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -1 (10:59:28.458) ~0.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+          <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -200px (10:20:09.051), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -background (10:44:24.231), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -200px (10:20:09.051) ~0.80, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -background (10:44:24.231) ~0.90, +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -123456 (10:19:55.544), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +654321 (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -123456 (10:19:55.544) ~0.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:17:06.867), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
+          <t>-&lt; (10:12:37.377), -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:17:06.867), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00)</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:22:03.455), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:22:03.455) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="n">
